--- a/books_bulk_upload_template.xlsx
+++ b/books_bulk_upload_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/e-library-ptec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F8E1660-A350-3749-A99E-68A8FDD8D16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD9D398-3FE7-8C45-ACC1-50F25A339368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{E14CBD72-5697-4946-AE2C-10235FB14B58}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E14CBD72-5697-4946-AE2C-10235FB14B58}"/>
   </bookViews>
   <sheets>
     <sheet name="books_bulk_upload_template" sheetId="1" r:id="rId1"/>
@@ -20,40 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>📁 pdfs/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-001.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-002.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-003.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-004.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-005.pdf</t>
-  </si>
-  <si>
-    <t>📁 covers/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-001.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-002.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-003.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  book-005.jpg</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>title</t>
   </si>
@@ -86,6 +53,39 @@
   </si>
   <si>
     <t>summary</t>
+  </si>
+  <si>
+    <t>1.A_Practical Research Methods - C.Dawson</t>
+  </si>
+  <si>
+    <t>A Practical Research Methods</t>
+  </si>
+  <si>
+    <t>Dr Catherine Dawson</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>1.A_Practical Research Methods - C.Dawson.pdf</t>
+  </si>
+  <si>
+    <t>Action Research in Teaching and Learning</t>
+  </si>
+  <si>
+    <t>2. Action Research in Teaching and Learning.pdf</t>
+  </si>
+  <si>
+    <t>2. Action Research in Teaching and Learning</t>
+  </si>
+  <si>
+    <t>Norton, Lin S</t>
+  </si>
+  <si>
+    <t>Education, Politics &amp; IR, Sociology &amp; Social Policy</t>
   </si>
 </sst>
 </file>
@@ -926,100 +926,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5467D9-B6D4-AA43-8D24-614251C7DAF6}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="6" max="6" width="54.6640625" customWidth="1"/>
+    <col min="7" max="7" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="I2">
+        <v>2002</v>
+      </c>
+      <c r="J2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="J3">
+        <v>285</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
